--- a/data/lexicon_review/Tunisian.xlsx
+++ b/data/lexicon_review/Tunisian.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
@@ -549,7 +549,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ana</t>
+          <t>ane</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
@@ -725,14 +725,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ena</t>
+          <t>ana</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
@@ -813,7 +813,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>eni</t>
+          <t>ena</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -830,7 +830,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
@@ -901,14 +901,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ane</t>
+          <t>eni</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
@@ -1165,7 +1165,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>estena</t>
+          <t>estana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
@@ -1273,12 +1273,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>stanna</t>
+          <t>istana</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>s</t>
@@ -1296,7 +1300,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>nn</t>
+          <t>n</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1337,7 +1341,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -1377,16 +1381,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>estana</t>
+          <t>stanna</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>s</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>nn</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
@@ -1485,14 +1485,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>istana</t>
+          <t>estena</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
@@ -1593,7 +1593,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>esstena</t>
+          <t>estanna</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ss</t>
+          <t>s</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>nn</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -1661,7 +1661,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
@@ -1701,7 +1701,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>estanna</t>
+          <t>esstena</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>ss</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>nn</t>
+          <t>n</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -1877,7 +1877,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>a5er</t>
+          <t>e5er</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>a5ar</t>
+          <t>a5er</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2125,7 +2125,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
@@ -2138,12 +2138,12 @@
           <t>خ</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -2157,14 +2157,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>e5er</t>
+          <t>a5ra</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
@@ -2230,12 +2230,12 @@
           <t>خ</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -2249,7 +2249,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>a5ra</t>
+          <t>a5ar</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
           <t>r</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>akhar</t>
+          <t>akher</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
@@ -2433,14 +2433,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ekher</t>
+          <t>akhér</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>é</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
@@ -2525,14 +2525,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>akher</t>
+          <t>ekher</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2617,7 +2617,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>akhér</t>
+          <t>akhar</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>é</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3161,7 +3161,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>eau</t>
+          <t>met</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
@@ -3237,7 +3237,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>maa</t>
+          <t>ma2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3252,12 +3252,12 @@
           <t>a</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
@@ -3381,12 +3381,24 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ء</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
@@ -3401,14 +3413,26 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>met</t>
+          <t>me2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
@@ -3477,7 +3501,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>me2</t>
+          <t>maa</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -3489,15 +3513,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
@@ -3533,24 +3557,12 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>ء</t>
-        </is>
-      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
@@ -3565,26 +3577,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ma2</t>
+          <t>eau</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
@@ -4213,22 +4213,22 @@
           <t>ر</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ئ</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>ئ</t>
+          <t>ي</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
           <t>س</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -4241,7 +4241,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ra2iss</t>
+          <t>raeiss</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4258,19 +4258,15 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>ei</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
           <t>ss</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -4305,7 +4301,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
@@ -4313,22 +4309,22 @@
           <t>ر</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
         <is>
           <t>ئ</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>س</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -4341,7 +4337,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>raeiss</t>
+          <t>ra2iss</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -4358,15 +4354,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ei</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
           <t>ss</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -4419,12 +4419,12 @@
           <t>ا</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -4437,7 +4437,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>soual</t>
+          <t>so2el</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -4449,20 +4449,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -4497,7 +4501,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
@@ -4515,12 +4519,12 @@
           <t>ا</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -4533,7 +4537,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>so2el</t>
+          <t>souel</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -4545,24 +4549,20 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
           <t>l</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>souel</t>
+          <t>soual</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
@@ -4825,7 +4825,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>sou2al</t>
+          <t>sou2el</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
@@ -4925,7 +4925,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sou2el</t>
+          <t>sou2al</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5101,14 +5101,14 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>istamel</t>
+          <t>est3mel</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -5221,14 +5221,14 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>est3mel</t>
+          <t>istamel</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -5293,7 +5293,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
@@ -5341,14 +5341,14 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>isti3mel</t>
+          <t>este3mel</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -5465,14 +5465,14 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>esta3mel</t>
+          <t>ista3mal</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ista3mal</t>
+          <t>iste3mel</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -5713,14 +5713,14 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>esti3mel</t>
+          <t>ista3mel</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
@@ -5807,12 +5807,12 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr">
+      <c r="G170" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>م</t>
@@ -5837,14 +5837,14 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>este3mel</t>
+          <t>istaamel</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
@@ -5931,12 +5931,12 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr">
+      <c r="G173" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>م</t>
@@ -5961,7 +5961,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>este3mal</t>
+          <t>estaamel</t>
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -5983,22 +5983,22 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
           <t>e</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
@@ -6055,12 +6055,12 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>م</t>
@@ -6085,7 +6085,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>estaamel</t>
+          <t>este3mal</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -6107,22 +6107,22 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
           <t>a</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>e</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
@@ -6209,7 +6209,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>esta3mal</t>
+          <t>esta3mel</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
@@ -6303,12 +6303,12 @@
           <t>ت</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>م</t>
@@ -6333,34 +6333,34 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>istaamel</t>
+          <t>esti3mel</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
       <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
           <t>i</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
@@ -6457,14 +6457,14 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ista3mel</t>
+          <t>esta3mal</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -6533,7 +6533,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
@@ -6581,44 +6581,44 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>esti3mal</t>
+          <t>isti3mel</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
           <t>e</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
@@ -6705,31 +6705,31 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>iste3mel</t>
+          <t>esti3mal</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
           <t>i</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>t</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
       <c r="H192" t="inlineStr">
         <is>
           <t>3</t>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -7333,7 +7333,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
@@ -7377,7 +7377,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>yaleebou</t>
+          <t>yal3abou</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -7394,12 +7394,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
@@ -7570,12 +7570,12 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
           <t>ب</t>
@@ -7601,7 +7601,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>yal3abou</t>
+          <t>yale3bou</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -7618,12 +7618,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -7682,12 +7682,12 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr"/>
       <c r="H218" t="inlineStr">
         <is>
           <t>ب</t>
@@ -7713,7 +7713,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>yale3bou</t>
+          <t>yaleebou</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
@@ -8081,12 +8081,12 @@
           <t>ط</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>ا</t>
@@ -8109,7 +8109,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>tayara</t>
+          <t>tayyar</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>yy</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -8139,11 +8139,7 @@
           <t>r</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
@@ -8177,7 +8173,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
@@ -8185,12 +8181,12 @@
           <t>ط</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>ا</t>
@@ -8213,7 +8209,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>tayyar</t>
+          <t>tayara</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -8230,7 +8226,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>yy</t>
+          <t>y</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -8243,7 +8239,11 @@
           <t>r</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
@@ -8309,19 +8309,19 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>7oma</t>
+          <t>hama</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -8369,7 +8369,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
@@ -8401,19 +8401,19 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>hama</t>
+          <t>7oma</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -8461,25 +8461,13 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C245" t="inlineStr"/>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>ح</t>
-        </is>
-      </c>
+      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>ى</t>
-        </is>
-      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
       <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr"/>
@@ -8493,31 +8481,15 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>7omma</t>
+          <t>s5ana</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="inlineStr"/>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
       <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr"/>
@@ -8649,13 +8621,25 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C251" t="inlineStr"/>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ح</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
-      <c r="G251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>ى</t>
+        </is>
+      </c>
       <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr"/>
@@ -8669,15 +8653,31 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>s5ana</t>
+          <t>homma</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
-      <c r="G252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr"/>
@@ -8713,7 +8713,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
@@ -8745,32 +8745,36 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>homma</t>
+          <t>7amya</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
@@ -8805,13 +8809,25 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ح</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>ى</t>
+        </is>
+      </c>
       <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr"/>
@@ -8825,15 +8841,31 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>broda</t>
+          <t>hamma</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
       <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr"/>
@@ -8869,7 +8901,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
@@ -8901,19 +8933,19 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>hamma</t>
+          <t>7omma</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -8964,22 +8996,10 @@
         <v>1</v>
       </c>
       <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>ح</t>
-        </is>
-      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>ى</t>
-        </is>
-      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
       <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr"/>
@@ -8993,36 +9013,16 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>7amya</t>
+          <t>broda</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr"/>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr"/>
@@ -9077,7 +9077,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>brouda</t>
+          <t>skhana</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr"/>
@@ -9141,7 +9141,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>skhana</t>
+          <t>brouda</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
@@ -9281,7 +9281,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>bab</t>
+          <t>beb</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -9293,7 +9293,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
@@ -9369,7 +9369,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>beb</t>
+          <t>bab</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -9693,15 +9693,39 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>ك</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
@@ -9713,17 +9737,41 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>bla9ar</t>
+          <t>plakar</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
       <c r="C291" t="inlineStr"/>
-      <c r="D291" t="inlineStr"/>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
-      <c r="I291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
@@ -9757,7 +9805,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
@@ -9801,14 +9849,14 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>placar</t>
+          <t>blakra</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>b</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9823,20 +9871,20 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
+          <t>k</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr"/>
@@ -9869,7 +9917,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
@@ -9913,7 +9961,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>plakar</t>
+          <t>placar</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -9935,7 +9983,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>c</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -9984,36 +10032,12 @@
         <v>1</v>
       </c>
       <c r="C299" t="inlineStr"/>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>ك</t>
-        </is>
-      </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr">
-        <is>
-          <t>ر</t>
-        </is>
-      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
@@ -10025,42 +10049,18 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>blakra</t>
+          <t>bla9ar</t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
       <c r="C300" t="inlineStr"/>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
       <c r="H300" t="inlineStr"/>
-      <c r="I300" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr"/>
@@ -10093,15 +10093,39 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C302" t="inlineStr"/>
-      <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
-      <c r="I302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>ك</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr"/>
@@ -10113,18 +10137,46 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>placard</t>
+          <t>blacare</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr"/>
-      <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
-      <c r="J303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
@@ -10157,7 +10209,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr"/>
@@ -10177,7 +10229,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>plakard</t>
+          <t>placard</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -10224,36 +10276,12 @@
         <v>1</v>
       </c>
       <c r="C308" t="inlineStr"/>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>ك</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>ر</t>
-        </is>
-      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr"/>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
@@ -10265,46 +10293,18 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>blacare</t>
+          <t>plakard</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr"/>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr"/>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr"/>
+      <c r="J309" t="inlineStr"/>
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr"/>
@@ -10401,25 +10401,13 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C314" t="inlineStr"/>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>ث</t>
-        </is>
-      </c>
+      <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr"/>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr"/>
@@ -10433,26 +10421,14 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>them</t>
+          <t>fama</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
       <c r="C315" t="inlineStr"/>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>th</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
       <c r="G315" t="inlineStr"/>
       <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr"/>
@@ -10577,13 +10553,25 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C320" t="inlineStr"/>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ث</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
-      <c r="G320" t="inlineStr"/>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
       <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr"/>
@@ -10597,14 +10585,26 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>fama</t>
+          <t>them</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
       <c r="C321" t="inlineStr"/>
-      <c r="D321" t="inlineStr"/>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>th</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="G321" t="inlineStr"/>
       <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr"/>
@@ -10641,13 +10641,25 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C323" t="inlineStr"/>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>ث</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
-      <c r="G323" t="inlineStr"/>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
       <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr"/>
@@ -10661,15 +10673,31 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>famma</t>
+          <t>thema</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="inlineStr"/>
-      <c r="D324" t="inlineStr"/>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
-      <c r="G324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>th</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr"/>
@@ -10705,7 +10733,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
@@ -10737,7 +10765,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>thema</t>
+          <t>thama</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -10749,7 +10777,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -10797,25 +10825,13 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C329" t="inlineStr"/>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>ث</t>
-        </is>
-      </c>
+      <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr"/>
@@ -10829,31 +10845,15 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>thama</t>
+          <t>famma</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr"/>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>th</t>
-        </is>
-      </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr"/>
       <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr"/>
@@ -10981,7 +10981,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
@@ -11017,7 +11017,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>jama3</t>
+          <t>jema3</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -11081,7 +11081,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
@@ -11117,7 +11117,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>jame3</t>
+          <t>jama3</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -11199,12 +11199,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr">
+      <c r="G341" t="inlineStr"/>
+      <c r="H341" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr"/>
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr"/>
@@ -11217,7 +11217,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>jamaa</t>
+          <t>jeme3</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
@@ -11299,12 +11299,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="inlineStr">
+      <c r="G344" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
+      <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr"/>
@@ -11317,7 +11317,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>jeme3</t>
+          <t>jemaa</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -11339,12 +11339,12 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
@@ -11381,7 +11381,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
@@ -11399,12 +11399,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
+      <c r="G347" t="inlineStr"/>
+      <c r="H347" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr"/>
@@ -11417,7 +11417,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>jemaa</t>
+          <t>jame3</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -11429,22 +11429,22 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
           <t>e</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I348" t="inlineStr"/>
@@ -11481,7 +11481,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
@@ -11499,12 +11499,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr">
+      <c r="G350" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
+      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr"/>
@@ -11517,7 +11517,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>jema3</t>
+          <t>jamaa</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
@@ -11677,7 +11677,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
@@ -11713,14 +11713,14 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>7aja</t>
+          <t>haja</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
@@ -11809,14 +11809,14 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>haja</t>
+          <t>7aja</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
@@ -11905,7 +11905,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>sbe7</t>
+          <t>sbeh</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
@@ -11965,7 +11965,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
@@ -12001,7 +12001,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>sbah</t>
+          <t>sba7</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H366" t="inlineStr"/>
@@ -12061,7 +12061,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
@@ -12097,7 +12097,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>sbeh</t>
+          <t>sbe7</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -12119,7 +12119,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H369" t="inlineStr"/>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
@@ -12193,7 +12193,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>sba7</t>
+          <t>sbah</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="H372" t="inlineStr"/>
@@ -12256,27 +12256,11 @@
         <v>1</v>
       </c>
       <c r="C374" t="inlineStr"/>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>ص</t>
-        </is>
-      </c>
-      <c r="E374" t="inlineStr">
-        <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>ح</t>
-        </is>
-      </c>
+      <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr"/>
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr"/>
@@ -12289,36 +12273,16 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>sbeeh</t>
+          <t>matin</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
       <c r="C375" t="inlineStr"/>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="E375" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H375" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr"/>
+      <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr"/>
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
@@ -12356,11 +12320,27 @@
         <v>1</v>
       </c>
       <c r="C377" t="inlineStr"/>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>ص</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>ح</t>
+        </is>
+      </c>
       <c r="I377" t="inlineStr"/>
       <c r="J377" t="inlineStr"/>
       <c r="K377" t="inlineStr"/>
@@ -12373,16 +12353,36 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>sober</t>
+          <t>saba7</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="inlineStr"/>
-      <c r="D378" t="inlineStr"/>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="I378" t="inlineStr"/>
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr"/>
@@ -12437,7 +12437,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>matin</t>
+          <t>sober</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -12489,17 +12489,17 @@
           <t>ص</t>
         </is>
       </c>
-      <c r="E383" t="inlineStr"/>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
           <t>ا</t>
         </is>
       </c>
+      <c r="G383" t="inlineStr"/>
       <c r="H383" t="inlineStr">
         <is>
           <t>ح</t>
@@ -12517,7 +12517,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>saba7</t>
+          <t>sbeeh</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -12529,22 +12529,22 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="I384" t="inlineStr"/>
@@ -12797,24 +12797,12 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>خ</t>
-        </is>
-      </c>
-      <c r="E395" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr">
-        <is>
-          <t>ك</t>
-        </is>
-      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
       <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr"/>
@@ -12829,26 +12817,14 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>khouk</t>
+          <t>khaki</t>
         </is>
       </c>
       <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr"/>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>kh</t>
-        </is>
-      </c>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
       <c r="G396" t="inlineStr"/>
       <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr"/>
@@ -12885,12 +12861,24 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C398" t="inlineStr"/>
-      <c r="D398" t="inlineStr"/>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>خ</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>ك</t>
+        </is>
+      </c>
       <c r="G398" t="inlineStr"/>
       <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr"/>
@@ -12905,14 +12893,26 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>khaki</t>
+          <t>khouk</t>
         </is>
       </c>
       <c r="B399" t="inlineStr"/>
       <c r="C399" t="inlineStr"/>
-      <c r="D399" t="inlineStr"/>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>kh</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="G399" t="inlineStr"/>
       <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr"/>
@@ -13157,7 +13157,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
@@ -13197,7 +13197,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>hedheka</t>
+          <t>hetheka</t>
         </is>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -13214,7 +13214,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>dh</t>
+          <t>th</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
@@ -13305,7 +13305,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>hadheka</t>
+          <t>hadhaka</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -13327,7 +13327,7 @@
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -13373,7 +13373,7 @@
         </is>
       </c>
       <c r="B413" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
@@ -13413,7 +13413,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>hetheka</t>
+          <t>hedheka</t>
         </is>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>dh</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
@@ -13481,7 +13481,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
@@ -13521,7 +13521,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>hadhaka</t>
+          <t>hatheka</t>
         </is>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -13538,12 +13538,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>dh</t>
+          <t>th</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -13589,7 +13589,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
@@ -13629,7 +13629,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>hatheka</t>
+          <t>hedhaka</t>
         </is>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -13641,17 +13641,17 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>dh</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
           <t>a</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>th</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>e</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -13697,7 +13697,7 @@
         </is>
       </c>
       <c r="B422" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
@@ -13737,7 +13737,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>hedhaka</t>
+          <t>hadheka</t>
         </is>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -13749,17 +13749,17 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>dh</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
           <t>e</t>
-        </is>
-      </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>dh</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -14205,7 +14205,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr">
@@ -14245,7 +14245,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>sahbi</t>
+          <t>sa7by</t>
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -14262,7 +14262,7 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
@@ -14272,7 +14272,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="I438" t="inlineStr"/>
@@ -14309,7 +14309,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
@@ -14349,7 +14349,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>sa7bi</t>
+          <t>sahby</t>
         </is>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="I441" t="inlineStr"/>
@@ -14413,7 +14413,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
@@ -14431,17 +14431,17 @@
           <t>ح</t>
         </is>
       </c>
-      <c r="G443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="I443" t="inlineStr">
-        <is>
           <t>ي</t>
         </is>
       </c>
+      <c r="I443" t="inlineStr"/>
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
@@ -14453,7 +14453,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>sahib</t>
+          <t>sahbi</t>
         </is>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -14475,12 +14475,12 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
           <t>i</t>
-        </is>
-      </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>b</t>
         </is>
       </c>
       <c r="I444" t="inlineStr"/>
@@ -14517,7 +14517,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
@@ -14557,7 +14557,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>sa7by</t>
+          <t>sa7bi</t>
         </is>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -14584,7 +14584,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="I447" t="inlineStr"/>
@@ -14639,17 +14639,17 @@
           <t>ح</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr">
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
         <is>
           <t>ب</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr">
+      <c r="I449" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="I449" t="inlineStr"/>
       <c r="J449" t="inlineStr"/>
       <c r="K449" t="inlineStr"/>
       <c r="L449" t="inlineStr"/>
@@ -14661,7 +14661,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>sahby</t>
+          <t>sahib</t>
         </is>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -14683,12 +14683,12 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
           <t>b</t>
-        </is>
-      </c>
-      <c r="H450" t="inlineStr">
-        <is>
-          <t>y</t>
         </is>
       </c>
       <c r="I450" t="inlineStr"/>
@@ -14803,12 +14803,12 @@
           <t>ح</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr">
+      <c r="G455" t="inlineStr">
         <is>
           <t>ك</t>
         </is>
       </c>
+      <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr"/>
       <c r="K455" t="inlineStr"/>
@@ -14821,19 +14821,19 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>4a7ek</t>
+          <t>dhe7k</t>
         </is>
       </c>
       <c r="B456" t="inlineStr"/>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>dh</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -14843,14 +14843,10 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H456" t="inlineStr">
-        <is>
           <t>k</t>
         </is>
       </c>
+      <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr"/>
       <c r="K456" t="inlineStr"/>
@@ -14885,7 +14881,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
@@ -14917,7 +14913,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>dhhak</t>
+          <t>dh7ak</t>
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -14929,7 +14925,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -15069,7 +15065,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
@@ -15077,12 +15073,12 @@
           <t>ض</t>
         </is>
       </c>
-      <c r="E464" t="inlineStr">
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
         <is>
           <t>ح</t>
         </is>
       </c>
-      <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
           <t>ك</t>
@@ -15101,7 +15097,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>dhhek</t>
+          <t>dhohk</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -15113,12 +15109,12 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
           <t>h</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>e</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
@@ -15175,12 +15171,12 @@
           <t>ح</t>
         </is>
       </c>
-      <c r="G467" t="inlineStr"/>
-      <c r="H467" t="inlineStr">
+      <c r="G467" t="inlineStr">
         <is>
           <t>ك</t>
         </is>
       </c>
+      <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr"/>
       <c r="J467" t="inlineStr"/>
       <c r="K467" t="inlineStr"/>
@@ -15193,36 +15189,32 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>dahek</t>
+          <t>dhi7k</t>
         </is>
       </c>
       <c r="B468" t="inlineStr"/>
       <c r="C468" t="inlineStr"/>
       <c r="D468" t="inlineStr">
         <is>
-          <t>d</t>
+          <t>dh</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="H468" t="inlineStr">
-        <is>
           <t>k</t>
         </is>
       </c>
+      <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr"/>
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr"/>
@@ -15257,7 +15249,7 @@
         </is>
       </c>
       <c r="B470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
@@ -15289,7 +15281,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>dh7ak</t>
+          <t>dhhek</t>
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -15301,12 +15293,12 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -15357,12 +15349,12 @@
           <t>ض</t>
         </is>
       </c>
-      <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr">
+      <c r="E473" t="inlineStr">
         <is>
           <t>ح</t>
         </is>
       </c>
+      <c r="F473" t="inlineStr"/>
       <c r="G473" t="inlineStr">
         <is>
           <t>ك</t>
@@ -15381,24 +15373,24 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>dhi7k</t>
+          <t>dhaka</t>
         </is>
       </c>
       <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>dh</t>
+          <t>d</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
@@ -15406,7 +15398,11 @@
           <t>k</t>
         </is>
       </c>
-      <c r="H474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="I474" t="inlineStr"/>
       <c r="J474" t="inlineStr"/>
       <c r="K474" t="inlineStr"/>
@@ -15541,18 +15537,18 @@
           <t>ض</t>
         </is>
       </c>
-      <c r="E479" t="inlineStr">
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr">
         <is>
           <t>ح</t>
         </is>
       </c>
-      <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr">
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr">
         <is>
           <t>ك</t>
         </is>
       </c>
-      <c r="H479" t="inlineStr"/>
       <c r="I479" t="inlineStr"/>
       <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr"/>
@@ -15565,7 +15561,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>dhaka</t>
+          <t>dahek</t>
         </is>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -15577,22 +15573,22 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
       <c r="G480" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
           <t>k</t>
-        </is>
-      </c>
-      <c r="H480" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="I480" t="inlineStr"/>
@@ -15629,7 +15625,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
@@ -15637,12 +15633,12 @@
           <t>ض</t>
         </is>
       </c>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr">
+      <c r="E482" t="inlineStr">
         <is>
           <t>ح</t>
         </is>
       </c>
+      <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr">
         <is>
           <t>ك</t>
@@ -15661,7 +15657,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>dhohk</t>
+          <t>dhhak</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -15673,12 +15669,12 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>h</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -15735,12 +15731,12 @@
           <t>ح</t>
         </is>
       </c>
-      <c r="G485" t="inlineStr">
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr">
         <is>
           <t>ك</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr"/>
       <c r="I485" t="inlineStr"/>
       <c r="J485" t="inlineStr"/>
       <c r="K485" t="inlineStr"/>
@@ -15753,32 +15749,36 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>dhe7k</t>
+          <t>4a7ek</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr">
         <is>
-          <t>dh</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
           <t>e</t>
         </is>
       </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G486" t="inlineStr">
+      <c r="H486" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr"/>
       <c r="I486" t="inlineStr"/>
       <c r="J486" t="inlineStr"/>
       <c r="K486" t="inlineStr"/>
@@ -15827,12 +15827,12 @@
           <t>ح</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr"/>
-      <c r="H488" t="inlineStr">
+      <c r="G488" t="inlineStr">
         <is>
           <t>ك</t>
         </is>
       </c>
+      <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr"/>
       <c r="J488" t="inlineStr"/>
       <c r="K488" t="inlineStr"/>
@@ -15845,7 +15845,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>dho7ek</t>
+          <t>dha7ka</t>
         </is>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -15857,7 +15857,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -15867,12 +15867,12 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>k</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I489" t="inlineStr"/>
@@ -15941,7 +15941,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>dhohek</t>
+          <t>dho7ek</t>
         </is>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -16005,7 +16005,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
@@ -16037,7 +16037,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>dhahik</t>
+          <t>dha7ek</t>
         </is>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -16054,12 +16054,12 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -16133,7 +16133,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>dhe7ek</t>
+          <t>dhahek</t>
         </is>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -16145,12 +16145,12 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -16211,12 +16211,12 @@
           <t>ح</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr">
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr">
         <is>
           <t>ك</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr"/>
       <c r="I500" t="inlineStr"/>
       <c r="J500" t="inlineStr"/>
       <c r="K500" t="inlineStr"/>
@@ -16229,7 +16229,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>dha7ka</t>
+          <t>dhe7ek</t>
         </is>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
           <t>k</t>
-        </is>
-      </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="I501" t="inlineStr"/>
@@ -16325,7 +16325,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>dhahek</t>
+          <t>dhahik</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
@@ -16389,7 +16389,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr">
@@ -16421,7 +16421,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>dha7ek</t>
+          <t>dhohek</t>
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
@@ -16433,12 +16433,12 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -16781,7 +16781,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C518" t="inlineStr"/>
       <c r="D518" t="inlineStr">
@@ -16817,7 +16817,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>ya3ti</t>
+          <t>yaati</t>
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
@@ -16829,7 +16829,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C521" t="inlineStr"/>
       <c r="D521" t="inlineStr">
@@ -16913,7 +16913,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>yaati</t>
+          <t>ya3ti</t>
         </is>
       </c>
       <c r="B522" t="inlineStr"/>
@@ -16925,7 +16925,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -17069,7 +17069,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C527" t="inlineStr"/>
       <c r="D527" t="inlineStr">
@@ -17077,17 +17077,17 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="E527" t="inlineStr">
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr">
         <is>
           <t>ظ</t>
         </is>
       </c>
-      <c r="F527" t="inlineStr">
+      <c r="G527" t="inlineStr">
         <is>
           <t>ه</t>
         </is>
       </c>
-      <c r="G527" t="inlineStr"/>
       <c r="H527" t="inlineStr">
         <is>
           <t>ر</t>
@@ -17113,25 +17113,29 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>dhaherli</t>
+          <t>yodhorli</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
       <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
           <t>dh</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr">
-        <is>
-          <t>ah</t>
-        </is>
-      </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -17181,7 +17185,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C530" t="inlineStr"/>
       <c r="D530" t="inlineStr">
@@ -17189,17 +17193,17 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="E530" t="inlineStr"/>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>ظ</t>
+        </is>
+      </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>ظ</t>
-        </is>
-      </c>
-      <c r="G530" t="inlineStr">
-        <is>
           <t>ه</t>
         </is>
       </c>
+      <c r="G530" t="inlineStr"/>
       <c r="H530" t="inlineStr">
         <is>
           <t>ر</t>
@@ -17225,29 +17229,25 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>yedhorli</t>
+          <t>dhaherli</t>
         </is>
       </c>
       <c r="B531" t="inlineStr"/>
       <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
+          <t>dh</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>ah</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
           <t>e</t>
-        </is>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>dh</t>
-        </is>
-      </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>o</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -17316,22 +17316,22 @@
           <t>ه</t>
         </is>
       </c>
-      <c r="H533" t="inlineStr">
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="I533" t="inlineStr">
+      <c r="J533" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="J533" t="inlineStr">
+      <c r="K533" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
       <c r="L533" t="inlineStr"/>
       <c r="M533" t="inlineStr"/>
       <c r="N533" t="inlineStr"/>
@@ -17341,7 +17341,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>yodhhrli</t>
+          <t>yo4horli</t>
         </is>
       </c>
       <c r="B534" t="inlineStr"/>
@@ -17358,7 +17358,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>dh</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -17368,20 +17368,24 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
           <t>r</t>
         </is>
       </c>
-      <c r="I534" t="inlineStr">
+      <c r="J534" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="J534" t="inlineStr">
+      <c r="K534" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
       <c r="L534" t="inlineStr"/>
       <c r="M534" t="inlineStr"/>
       <c r="N534" t="inlineStr"/>
@@ -17413,7 +17417,7 @@
         </is>
       </c>
       <c r="B536" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
@@ -17457,7 +17461,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>yodhorli</t>
+          <t>yedhorli</t>
         </is>
       </c>
       <c r="B537" t="inlineStr"/>
@@ -17469,7 +17473,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -17548,22 +17552,22 @@
           <t>ه</t>
         </is>
       </c>
-      <c r="H539" t="inlineStr"/>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>ر</t>
+          <t>ل</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="K539" t="inlineStr">
-        <is>
           <t>ي</t>
         </is>
       </c>
+      <c r="K539" t="inlineStr"/>
       <c r="L539" t="inlineStr"/>
       <c r="M539" t="inlineStr"/>
       <c r="N539" t="inlineStr"/>
@@ -17573,7 +17577,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>yo4horli</t>
+          <t>yodhhrli</t>
         </is>
       </c>
       <c r="B540" t="inlineStr"/>
@@ -17590,7 +17594,7 @@
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>dh</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -17600,24 +17604,20 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>r</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>l</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="K540" t="inlineStr">
-        <is>
           <t>i</t>
         </is>
       </c>
+      <c r="K540" t="inlineStr"/>
       <c r="L540" t="inlineStr"/>
       <c r="M540" t="inlineStr"/>
       <c r="N540" t="inlineStr"/>
@@ -17693,7 +17693,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>yodhherly</t>
+          <t>yethhorli</t>
         </is>
       </c>
       <c r="B543" t="inlineStr"/>
@@ -17705,24 +17705,24 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>th</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
           <t>o</t>
         </is>
       </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>dh</t>
-        </is>
-      </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="H543" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
       <c r="I543" t="inlineStr">
         <is>
           <t>r</t>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="K543" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="L543" t="inlineStr"/>
@@ -17769,7 +17769,7 @@
         </is>
       </c>
       <c r="B545" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr">
@@ -17813,7 +17813,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>yodhhorli</t>
+          <t>yodhherli</t>
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>e</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -17889,7 +17889,7 @@
         </is>
       </c>
       <c r="B548" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
@@ -17933,7 +17933,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>yodhherli</t>
+          <t>yodhherly</t>
         </is>
       </c>
       <c r="B549" t="inlineStr"/>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="K549" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="L549" t="inlineStr"/>
@@ -18009,7 +18009,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
@@ -18053,7 +18053,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>yethhorli</t>
+          <t>yodhhorli</t>
         </is>
       </c>
       <c r="B552" t="inlineStr"/>
@@ -18065,12 +18065,12 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>o</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>dh</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -18138,12 +18138,12 @@
         </is>
       </c>
       <c r="E554" t="inlineStr"/>
-      <c r="F554" t="inlineStr">
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr">
         <is>
           <t>ظ</t>
         </is>
       </c>
-      <c r="G554" t="inlineStr"/>
       <c r="H554" t="inlineStr">
         <is>
           <t>ه</t>
@@ -18173,7 +18173,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>yodh horli</t>
+          <t>youdhhorli</t>
         </is>
       </c>
       <c r="B555" t="inlineStr"/>
@@ -18190,12 +18190,12 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
           <t>dh</t>
-        </is>
-      </c>
-      <c r="G555" t="inlineStr">
-        <is>
-          <t> </t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -18262,12 +18262,12 @@
         </is>
       </c>
       <c r="E557" t="inlineStr"/>
-      <c r="F557" t="inlineStr"/>
-      <c r="G557" t="inlineStr">
+      <c r="F557" t="inlineStr">
         <is>
           <t>ظ</t>
         </is>
       </c>
+      <c r="G557" t="inlineStr"/>
       <c r="H557" t="inlineStr">
         <is>
           <t>ه</t>
@@ -18297,7 +18297,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>youdhhorli</t>
+          <t>yodh horli</t>
         </is>
       </c>
       <c r="B558" t="inlineStr"/>
@@ -18314,12 +18314,12 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>u</t>
+          <t>dh</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>dh</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -18397,22 +18397,22 @@
         </is>
       </c>
       <c r="H560" t="inlineStr"/>
-      <c r="I560" t="inlineStr">
+      <c r="I560" t="inlineStr"/>
+      <c r="J560" t="inlineStr">
         <is>
           <t>ر</t>
         </is>
       </c>
-      <c r="J560" t="inlineStr">
+      <c r="K560" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr">
+      <c r="L560" t="inlineStr">
         <is>
           <t>ي</t>
         </is>
       </c>
-      <c r="L560" t="inlineStr"/>
       <c r="M560" t="inlineStr"/>
       <c r="N560" t="inlineStr"/>
       <c r="O560" t="inlineStr"/>
@@ -18421,7 +18421,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>yodhehorli</t>
+          <t>yothhourli</t>
         </is>
       </c>
       <c r="B561" t="inlineStr"/>
@@ -18438,12 +18438,12 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>dh</t>
+          <t>th</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>eh</t>
+          <t>h</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -18453,20 +18453,24 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
+          <t>u</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
           <t>r</t>
         </is>
       </c>
-      <c r="J561" t="inlineStr">
+      <c r="K561" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr">
+      <c r="L561" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="L561" t="inlineStr"/>
       <c r="M561" t="inlineStr"/>
       <c r="N561" t="inlineStr"/>
       <c r="O561" t="inlineStr"/>
@@ -18497,7 +18501,7 @@
         </is>
       </c>
       <c r="B563" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr">
@@ -18511,12 +18515,12 @@
           <t>ظ</t>
         </is>
       </c>
-      <c r="G563" t="inlineStr">
+      <c r="G563" t="inlineStr"/>
+      <c r="H563" t="inlineStr">
         <is>
           <t>ه</t>
         </is>
       </c>
-      <c r="H563" t="inlineStr"/>
       <c r="I563" t="inlineStr"/>
       <c r="J563" t="inlineStr">
         <is>
@@ -18541,7 +18545,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>yothhourli</t>
+          <t>yodh'horli</t>
         </is>
       </c>
       <c r="B564" t="inlineStr"/>
@@ -18558,22 +18562,22 @@
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>th</t>
+          <t>dh</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr">
+      <c r="I564" t="inlineStr">
         <is>
           <t>o</t>
-        </is>
-      </c>
-      <c r="I564" t="inlineStr">
-        <is>
-          <t>u</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
@@ -18621,7 +18625,7 @@
         </is>
       </c>
       <c r="B566" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C566" t="inlineStr"/>
       <c r="D566" t="inlineStr">
@@ -18635,28 +18639,28 @@
           <t>ظ</t>
         </is>
       </c>
-      <c r="G566" t="inlineStr"/>
-      <c r="H566" t="inlineStr">
+      <c r="G566" t="inlineStr">
         <is>
           <t>ه</t>
         </is>
       </c>
-      <c r="I566" t="inlineStr"/>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>ر</t>
+        </is>
+      </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>ر</t>
+          <t>ل</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="L566" t="inlineStr">
-        <is>
           <t>ي</t>
         </is>
       </c>
+      <c r="L566" t="inlineStr"/>
       <c r="M566" t="inlineStr"/>
       <c r="N566" t="inlineStr"/>
       <c r="O566" t="inlineStr"/>
@@ -18665,7 +18669,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>yodh'horli</t>
+          <t>yodhehorli</t>
         </is>
       </c>
       <c r="B567" t="inlineStr"/>
@@ -18687,34 +18691,30 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>'</t>
+          <t>eh</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>o</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>r</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>l</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
         <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="L567" t="inlineStr">
-        <is>
           <t>i</t>
         </is>
       </c>
+      <c r="L567" t="inlineStr"/>
       <c r="M567" t="inlineStr"/>
       <c r="N567" t="inlineStr"/>
       <c r="O567" t="inlineStr"/>
@@ -18937,30 +18937,14 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>غ</t>
-        </is>
-      </c>
+      <c r="D575" t="inlineStr"/>
       <c r="E575" t="inlineStr"/>
-      <c r="F575" t="inlineStr">
-        <is>
-          <t>د</t>
-        </is>
-      </c>
-      <c r="G575" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="H575" t="inlineStr">
-        <is>
-          <t>ة</t>
-        </is>
-      </c>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr"/>
       <c r="I575" t="inlineStr"/>
       <c r="J575" t="inlineStr"/>
       <c r="K575" t="inlineStr"/>
@@ -18973,36 +18957,16 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>8odwa</t>
+          <t>4odwa</t>
         </is>
       </c>
       <c r="B576" t="inlineStr"/>
       <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E576" t="inlineStr">
-        <is>
-          <t>o</t>
-        </is>
-      </c>
-      <c r="F576" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="G576" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="H576" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="D576" t="inlineStr"/>
+      <c r="E576" t="inlineStr"/>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr"/>
       <c r="I576" t="inlineStr"/>
       <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr"/>
@@ -19037,7 +19001,7 @@
         </is>
       </c>
       <c r="B578" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
@@ -19073,7 +19037,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>8odoi</t>
+          <t>8odwa</t>
         </is>
       </c>
       <c r="B579" t="inlineStr"/>
@@ -19095,12 +19059,12 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>w</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
@@ -19140,11 +19104,27 @@
         <v>1</v>
       </c>
       <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>غ</t>
+        </is>
+      </c>
       <c r="E581" t="inlineStr"/>
-      <c r="F581" t="inlineStr"/>
-      <c r="G581" t="inlineStr"/>
-      <c r="H581" t="inlineStr"/>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>د</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
       <c r="I581" t="inlineStr"/>
       <c r="J581" t="inlineStr"/>
       <c r="K581" t="inlineStr"/>
@@ -19157,16 +19137,36 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>4odwa</t>
+          <t>8odoi</t>
         </is>
       </c>
       <c r="B582" t="inlineStr"/>
       <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
-      <c r="F582" t="inlineStr"/>
-      <c r="G582" t="inlineStr"/>
-      <c r="H582" t="inlineStr"/>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
       <c r="I582" t="inlineStr"/>
       <c r="J582" t="inlineStr"/>
       <c r="K582" t="inlineStr"/>
@@ -19201,7 +19201,7 @@
         </is>
       </c>
       <c r="B584" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
@@ -19237,7 +19237,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>ghodwa</t>
+          <t>ghodoi</t>
         </is>
       </c>
       <c r="B585" t="inlineStr"/>
@@ -19259,12 +19259,12 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>w</t>
+          <t>o</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>i</t>
         </is>
       </c>
       <c r="I585" t="inlineStr"/>
@@ -19301,7 +19301,7 @@
         </is>
       </c>
       <c r="B587" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
@@ -19337,7 +19337,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>ghodoi</t>
+          <t>ghodwa</t>
         </is>
       </c>
       <c r="B588" t="inlineStr"/>
@@ -19359,12 +19359,12 @@
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>w</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I588" t="inlineStr"/>
@@ -19701,29 +19701,13 @@
         </is>
       </c>
       <c r="B599" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C599" t="inlineStr"/>
-      <c r="D599" t="inlineStr">
-        <is>
-          <t>ف</t>
-        </is>
-      </c>
-      <c r="E599" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="F599" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="G599" t="inlineStr">
-        <is>
-          <t>س</t>
-        </is>
-      </c>
+      <c r="D599" t="inlineStr"/>
+      <c r="E599" t="inlineStr"/>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr"/>
       <c r="H599" t="inlineStr"/>
       <c r="I599" t="inlineStr"/>
       <c r="J599" t="inlineStr"/>
@@ -19737,31 +19721,15 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>flouss</t>
+          <t>argent</t>
         </is>
       </c>
       <c r="B600" t="inlineStr"/>
       <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="E600" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="F600" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
-      <c r="G600" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
+      <c r="D600" t="inlineStr"/>
+      <c r="E600" t="inlineStr"/>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
       <c r="H600" t="inlineStr"/>
       <c r="I600" t="inlineStr"/>
       <c r="J600" t="inlineStr"/>
@@ -19797,13 +19765,29 @@
         </is>
       </c>
       <c r="B602" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
-      <c r="E602" t="inlineStr"/>
-      <c r="F602" t="inlineStr"/>
-      <c r="G602" t="inlineStr"/>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>ف</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
       <c r="H602" t="inlineStr"/>
       <c r="I602" t="inlineStr"/>
       <c r="J602" t="inlineStr"/>
@@ -19817,15 +19801,31 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>argent</t>
+          <t>flouss</t>
         </is>
       </c>
       <c r="B603" t="inlineStr"/>
       <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr"/>
-      <c r="E603" t="inlineStr"/>
-      <c r="F603" t="inlineStr"/>
-      <c r="G603" t="inlineStr"/>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>f</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>ss</t>
+        </is>
+      </c>
       <c r="H603" t="inlineStr"/>
       <c r="I603" t="inlineStr"/>
       <c r="J603" t="inlineStr"/>
@@ -19861,7 +19861,7 @@
         </is>
       </c>
       <c r="B605" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C605" t="inlineStr"/>
       <c r="D605" t="inlineStr">
@@ -19909,19 +19909,19 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>véranda</t>
+          <t>firanda</t>
         </is>
       </c>
       <c r="B606" t="inlineStr"/>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
-          <t>v</t>
+          <t>f</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>é</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
@@ -20101,7 +20101,7 @@
         </is>
       </c>
       <c r="B611" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr">
@@ -20149,19 +20149,19 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>firanda</t>
+          <t>veranda</t>
         </is>
       </c>
       <c r="B612" t="inlineStr"/>
       <c r="C612" t="inlineStr"/>
       <c r="D612" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>v</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
@@ -20269,7 +20269,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>veranda</t>
+          <t>véranda</t>
         </is>
       </c>
       <c r="B615" t="inlineStr"/>
@@ -20281,7 +20281,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>é</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
@@ -20501,7 +20501,7 @@
         </is>
       </c>
       <c r="B623" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
@@ -20537,14 +20537,14 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>9dim</t>
+          <t>kdim</t>
         </is>
       </c>
       <c r="B624" t="inlineStr"/>
       <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>k</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
@@ -20597,7 +20597,7 @@
         </is>
       </c>
       <c r="B626" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
@@ -20633,14 +20633,14 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>kdim</t>
+          <t>9dim</t>
         </is>
       </c>
       <c r="B627" t="inlineStr"/>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>k</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
@@ -21601,7 +21601,7 @@
         </is>
       </c>
       <c r="B659" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
@@ -21633,7 +21633,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>heka</t>
+          <t>hika</t>
         </is>
       </c>
       <c r="B660" t="inlineStr"/>
@@ -21645,7 +21645,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -21693,7 +21693,7 @@
         </is>
       </c>
       <c r="B662" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C662" t="inlineStr"/>
       <c r="D662" t="inlineStr">
@@ -21725,7 +21725,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>hika</t>
+          <t>heka</t>
         </is>
       </c>
       <c r="B663" t="inlineStr"/>
@@ -21737,7 +21737,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
@@ -22008,31 +22008,11 @@
         <v>1</v>
       </c>
       <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr">
-        <is>
-          <t>ب</t>
-        </is>
-      </c>
-      <c r="E674" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="F674" t="inlineStr">
-        <is>
-          <t>ه</t>
-        </is>
-      </c>
-      <c r="G674" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="H674" t="inlineStr">
-        <is>
-          <t>ة</t>
-        </is>
-      </c>
+      <c r="D674" t="inlineStr"/>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr"/>
+      <c r="H674" t="inlineStr"/>
       <c r="I674" t="inlineStr"/>
       <c r="J674" t="inlineStr"/>
       <c r="K674" t="inlineStr"/>
@@ -22045,32 +22025,16 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>behi</t>
+          <t>bien</t>
         </is>
       </c>
       <c r="B675" t="inlineStr"/>
       <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="E675" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="F675" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
+      <c r="D675" t="inlineStr"/>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="inlineStr"/>
       <c r="G675" t="inlineStr"/>
-      <c r="H675" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
+      <c r="H675" t="inlineStr"/>
       <c r="I675" t="inlineStr"/>
       <c r="J675" t="inlineStr"/>
       <c r="K675" t="inlineStr"/>
@@ -22145,7 +22109,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>bahi</t>
+          <t>behi</t>
         </is>
       </c>
       <c r="B678" t="inlineStr"/>
@@ -22157,7 +22121,7 @@
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
@@ -22208,11 +22172,31 @@
         <v>1</v>
       </c>
       <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
-      <c r="E680" t="inlineStr"/>
-      <c r="F680" t="inlineStr"/>
-      <c r="G680" t="inlineStr"/>
-      <c r="H680" t="inlineStr"/>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>ه</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
       <c r="I680" t="inlineStr"/>
       <c r="J680" t="inlineStr"/>
       <c r="K680" t="inlineStr"/>
@@ -22225,16 +22209,32 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>bien</t>
+          <t>bahi</t>
         </is>
       </c>
       <c r="B681" t="inlineStr"/>
       <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr"/>
-      <c r="E681" t="inlineStr"/>
-      <c r="F681" t="inlineStr"/>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
       <c r="G681" t="inlineStr"/>
-      <c r="H681" t="inlineStr"/>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
       <c r="I681" t="inlineStr"/>
       <c r="J681" t="inlineStr"/>
       <c r="K681" t="inlineStr"/>
@@ -22309,7 +22309,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>bahia</t>
+          <t>bahya</t>
         </is>
       </c>
       <c r="B684" t="inlineStr"/>
@@ -22331,7 +22331,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
@@ -22373,7 +22373,7 @@
         </is>
       </c>
       <c r="B686" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C686" t="inlineStr"/>
       <c r="D686" t="inlineStr">
@@ -22413,7 +22413,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>behia</t>
+          <t>behya</t>
         </is>
       </c>
       <c r="B687" t="inlineStr"/>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -22517,7 +22517,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>bahya</t>
+          <t>bahia</t>
         </is>
       </c>
       <c r="B690" t="inlineStr"/>
@@ -22539,7 +22539,7 @@
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
@@ -22581,7 +22581,7 @@
         </is>
       </c>
       <c r="B692" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C692" t="inlineStr"/>
       <c r="D692" t="inlineStr">
@@ -22621,7 +22621,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>behya</t>
+          <t>behia</t>
         </is>
       </c>
       <c r="B693" t="inlineStr"/>
@@ -22643,7 +22643,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
@@ -22708,12 +22708,12 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="H695" t="inlineStr"/>
-      <c r="I695" t="inlineStr">
+      <c r="H695" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
+      <c r="I695" t="inlineStr"/>
       <c r="J695" t="inlineStr"/>
       <c r="K695" t="inlineStr"/>
       <c r="L695" t="inlineStr"/>
@@ -22725,7 +22725,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>bahiya</t>
+          <t>behyaa</t>
         </is>
       </c>
       <c r="B696" t="inlineStr"/>
@@ -22737,29 +22737,25 @@
       </c>
       <c r="E696" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>ya</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F696" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="G696" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="H696" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="I696" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="I696" t="inlineStr"/>
       <c r="J696" t="inlineStr"/>
       <c r="K696" t="inlineStr"/>
       <c r="L696" t="inlineStr"/>
@@ -22793,7 +22789,7 @@
         </is>
       </c>
       <c r="B698" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C698" t="inlineStr"/>
       <c r="D698" t="inlineStr">
@@ -22816,12 +22812,12 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="H698" t="inlineStr">
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
-      <c r="I698" t="inlineStr"/>
       <c r="J698" t="inlineStr"/>
       <c r="K698" t="inlineStr"/>
       <c r="L698" t="inlineStr"/>
@@ -22833,7 +22829,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>behyaa</t>
+          <t>behiya</t>
         </is>
       </c>
       <c r="B699" t="inlineStr"/>
@@ -22855,15 +22851,19 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>ya</t>
+          <t>i</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
           <t>a</t>
         </is>
       </c>
-      <c r="I699" t="inlineStr"/>
       <c r="J699" t="inlineStr"/>
       <c r="K699" t="inlineStr"/>
       <c r="L699" t="inlineStr"/>
@@ -22897,7 +22897,7 @@
         </is>
       </c>
       <c r="B701" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C701" t="inlineStr"/>
       <c r="D701" t="inlineStr">
@@ -22937,7 +22937,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>behiya</t>
+          <t>bahiya</t>
         </is>
       </c>
       <c r="B702" t="inlineStr"/>
@@ -22949,7 +22949,7 @@
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
@@ -23271,7 +23271,7 @@
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J714" t="inlineStr"/>
@@ -23396,40 +23396,132 @@
         <v>1</v>
       </c>
       <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
-      <c r="F716" t="inlineStr"/>
-      <c r="G716" t="inlineStr"/>
-      <c r="H716" t="inlineStr"/>
-      <c r="I716" t="inlineStr"/>
-      <c r="J716" t="inlineStr"/>
-      <c r="K716" t="inlineStr"/>
-      <c r="L716" t="inlineStr"/>
-      <c r="M716" t="inlineStr"/>
-      <c r="N716" t="inlineStr"/>
-      <c r="O716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>ج</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>ح</t>
+        </is>
+      </c>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
       <c r="P716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>joint l7ouma</t>
+          <t>jnint l7ouma</t>
         </is>
       </c>
       <c r="B717" t="inlineStr"/>
       <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
-      <c r="F717" t="inlineStr"/>
-      <c r="G717" t="inlineStr"/>
-      <c r="H717" t="inlineStr"/>
-      <c r="I717" t="inlineStr"/>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>j</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="J717" t="inlineStr"/>
-      <c r="K717" t="inlineStr"/>
-      <c r="L717" t="inlineStr"/>
-      <c r="M717" t="inlineStr"/>
-      <c r="N717" t="inlineStr"/>
-      <c r="O717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
       <c r="P717" t="inlineStr"/>
     </row>
     <row r="718">
@@ -23487,7 +23579,7 @@
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
@@ -23525,7 +23617,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>jnint l7ouma</t>
+          <t>jninet 7ouma</t>
         </is>
       </c>
       <c r="B720" t="inlineStr"/>
@@ -23552,20 +23644,16 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>et</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J720" t="inlineStr"/>
-      <c r="K720" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
+      <c r="K720" t="inlineStr"/>
       <c r="L720" t="inlineStr">
         <is>
           <t>7</t>
@@ -23616,128 +23704,40 @@
         <v>1</v>
       </c>
       <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr">
-        <is>
-          <t>ج</t>
-        </is>
-      </c>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>ن</t>
-        </is>
-      </c>
-      <c r="F722" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="G722" t="inlineStr">
-        <is>
-          <t>ن</t>
-        </is>
-      </c>
-      <c r="H722" t="inlineStr">
-        <is>
-          <t>ة</t>
-        </is>
-      </c>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J722" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="K722" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="L722" t="inlineStr">
-        <is>
-          <t>ح</t>
-        </is>
-      </c>
-      <c r="M722" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="N722" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="O722" t="inlineStr">
-        <is>
-          <t>ة</t>
-        </is>
-      </c>
+      <c r="D722" t="inlineStr"/>
+      <c r="E722" t="inlineStr"/>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="inlineStr"/>
+      <c r="J722" t="inlineStr"/>
+      <c r="K722" t="inlineStr"/>
+      <c r="L722" t="inlineStr"/>
+      <c r="M722" t="inlineStr"/>
+      <c r="N722" t="inlineStr"/>
+      <c r="O722" t="inlineStr"/>
       <c r="P722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>jninet 7ouma</t>
+          <t>joint l7ouma</t>
         </is>
       </c>
       <c r="B723" t="inlineStr"/>
       <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr">
-        <is>
-          <t>j</t>
-        </is>
-      </c>
-      <c r="E723" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="F723" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="G723" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="H723" t="inlineStr">
-        <is>
-          <t>et</t>
-        </is>
-      </c>
-      <c r="I723" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
+      <c r="D723" t="inlineStr"/>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
       <c r="J723" t="inlineStr"/>
       <c r="K723" t="inlineStr"/>
-      <c r="L723" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="M723" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
-      <c r="N723" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="O723" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
+      <c r="L723" t="inlineStr"/>
+      <c r="M723" t="inlineStr"/>
+      <c r="N723" t="inlineStr"/>
+      <c r="O723" t="inlineStr"/>
       <c r="P723" t="inlineStr"/>
     </row>
     <row r="724">
@@ -23765,7 +23765,7 @@
         </is>
       </c>
       <c r="B725" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
@@ -23833,7 +23833,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>jninet lhouma</t>
+          <t>jninet il7oma</t>
         </is>
       </c>
       <c r="B726" t="inlineStr"/>
@@ -23865,10 +23865,14 @@
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J726" t="inlineStr"/>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
       <c r="K726" t="inlineStr">
         <is>
           <t>l</t>
@@ -23876,12 +23880,12 @@
       </c>
       <c r="L726" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M726" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>o</t>
         </is>
       </c>
       <c r="N726" t="inlineStr">
@@ -23921,7 +23925,7 @@
         </is>
       </c>
       <c r="B728" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
@@ -23951,7 +23955,7 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
@@ -23989,7 +23993,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>jninet il7oma</t>
+          <t>jninet lhouma</t>
         </is>
       </c>
       <c r="B729" t="inlineStr"/>
@@ -24021,14 +24025,10 @@
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J729" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr"/>
       <c r="K729" t="inlineStr">
         <is>
           <t>l</t>
@@ -24036,12 +24036,12 @@
       </c>
       <c r="L729" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="M729" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="N729" t="inlineStr">
@@ -24104,27 +24104,27 @@
           <t>ن</t>
         </is>
       </c>
-      <c r="H731" t="inlineStr">
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
-      <c r="I731" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="J731" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
           <t>ا</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr">
+      <c r="L731" t="inlineStr">
         <is>
           <t>ل</t>
         </is>
       </c>
-      <c r="L731" t="inlineStr"/>
       <c r="M731" t="inlineStr">
         <is>
           <t>ح</t>
@@ -24149,7 +24149,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>jninet el homa</t>
+          <t>jninit alhouma</t>
         </is>
       </c>
       <c r="B732" t="inlineStr"/>
@@ -24176,29 +24176,29 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>i</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t> </t>
+          <t>t</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>e</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="L732" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="L732" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
       <c r="M732" t="inlineStr">
         <is>
           <t>h</t>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="N732" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="O732" t="inlineStr">
@@ -24268,27 +24268,27 @@
           <t>ن</t>
         </is>
       </c>
-      <c r="H734" t="inlineStr"/>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>ة</t>
+        </is>
+      </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>ة</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t> </t>
+          <t>ا</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="L734" t="inlineStr">
-        <is>
           <t>ل</t>
         </is>
       </c>
+      <c r="L734" t="inlineStr"/>
       <c r="M734" t="inlineStr">
         <is>
           <t>ح</t>
@@ -24313,7 +24313,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>jninit alhouma</t>
+          <t>jninet el homa</t>
         </is>
       </c>
       <c r="B735" t="inlineStr"/>
@@ -24340,27 +24340,27 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>et</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>t</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t> </t>
+          <t>e</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>l</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
         <is>
-          <t>l</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M735" t="inlineStr">
@@ -24370,7 +24370,7 @@
       </c>
       <c r="N735" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>o</t>
         </is>
       </c>
       <c r="O735" t="inlineStr">
@@ -24409,7 +24409,7 @@
         </is>
       </c>
       <c r="B737" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
@@ -24452,32 +24452,32 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="L737" t="inlineStr"/>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>ح</t>
+        </is>
+      </c>
       <c r="M737" t="inlineStr">
         <is>
-          <t>ح</t>
+          <t>و</t>
         </is>
       </c>
       <c r="N737" t="inlineStr">
         <is>
-          <t>و</t>
+          <t>م</t>
         </is>
       </c>
       <c r="O737" t="inlineStr">
         <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="P737" t="inlineStr">
-        <is>
           <t>ة</t>
         </is>
       </c>
+      <c r="P737" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>jninet l 7ouma</t>
+          <t>jninat el7ouma</t>
         </is>
       </c>
       <c r="B738" t="inlineStr"/>
@@ -24504,15 +24504,19 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>et</t>
+          <t>at</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J738" t="inlineStr"/>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="K738" t="inlineStr">
         <is>
           <t>l</t>
@@ -24520,29 +24524,25 @@
       </c>
       <c r="L738" t="inlineStr">
         <is>
-          <t> </t>
+          <t>7</t>
         </is>
       </c>
       <c r="M738" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>ou</t>
         </is>
       </c>
       <c r="N738" t="inlineStr">
         <is>
-          <t>ou</t>
+          <t>m</t>
         </is>
       </c>
       <c r="O738" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="P738" t="inlineStr">
-        <is>
           <t>a</t>
         </is>
       </c>
+      <c r="P738" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr"/>
@@ -24600,7 +24600,7 @@
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
@@ -24674,7 +24674,7 @@
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
@@ -24763,7 +24763,7 @@
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
@@ -24801,7 +24801,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>jninat el7ouma</t>
+          <t>jninet el7ouma</t>
         </is>
       </c>
       <c r="B744" t="inlineStr"/>
@@ -24828,12 +24828,12 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>et</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
@@ -24893,7 +24893,7 @@
         </is>
       </c>
       <c r="B746" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C746" t="inlineStr"/>
       <c r="D746" t="inlineStr">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
@@ -24936,32 +24936,32 @@
           <t>ل</t>
         </is>
       </c>
-      <c r="L746" t="inlineStr">
+      <c r="L746" t="inlineStr"/>
+      <c r="M746" t="inlineStr">
         <is>
           <t>ح</t>
         </is>
       </c>
-      <c r="M746" t="inlineStr">
+      <c r="N746" t="inlineStr">
         <is>
           <t>و</t>
         </is>
       </c>
-      <c r="N746" t="inlineStr">
+      <c r="O746" t="inlineStr">
         <is>
           <t>م</t>
         </is>
       </c>
-      <c r="O746" t="inlineStr">
+      <c r="P746" t="inlineStr">
         <is>
           <t>ة</t>
         </is>
       </c>
-      <c r="P746" t="inlineStr"/>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>jninet el7ouma</t>
+          <t>jninet l 7ouma</t>
         </is>
       </c>
       <c r="B747" t="inlineStr"/>
@@ -24993,14 +24993,10 @@
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="J747" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr"/>
       <c r="K747" t="inlineStr">
         <is>
           <t>l</t>
@@ -25008,25 +25004,29 @@
       </c>
       <c r="L747" t="inlineStr">
         <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M747" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="M747" t="inlineStr">
+      <c r="N747" t="inlineStr">
         <is>
           <t>ou</t>
         </is>
       </c>
-      <c r="N747" t="inlineStr">
+      <c r="O747" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O747" t="inlineStr">
+      <c r="P747" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="P747" t="inlineStr"/>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr"/>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
@@ -25153,7 +25153,7 @@
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
@@ -25168,7 +25168,7 @@
       </c>
       <c r="L750" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M750" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
@@ -25317,7 +25317,7 @@
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
@@ -25332,7 +25332,7 @@
       </c>
       <c r="L753" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="M753" t="inlineStr">
@@ -25384,11 +25384,31 @@
         <v>1</v>
       </c>
       <c r="C755" t="inlineStr"/>
-      <c r="D755" t="inlineStr"/>
-      <c r="E755" t="inlineStr"/>
-      <c r="F755" t="inlineStr"/>
-      <c r="G755" t="inlineStr"/>
-      <c r="H755" t="inlineStr"/>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>ل</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
       <c r="I755" t="inlineStr"/>
       <c r="J755" t="inlineStr"/>
       <c r="K755" t="inlineStr"/>
@@ -25401,16 +25421,28 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>alan</t>
+          <t>loun</t>
         </is>
       </c>
       <c r="B756" t="inlineStr"/>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr"/>
-      <c r="E756" t="inlineStr"/>
-      <c r="F756" t="inlineStr"/>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>l</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
       <c r="G756" t="inlineStr"/>
-      <c r="H756" t="inlineStr"/>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
       <c r="I756" t="inlineStr"/>
       <c r="J756" t="inlineStr"/>
       <c r="K756" t="inlineStr"/>
@@ -25448,31 +25480,11 @@
         <v>1</v>
       </c>
       <c r="C758" t="inlineStr"/>
-      <c r="D758" t="inlineStr">
-        <is>
-          <t>أ</t>
-        </is>
-      </c>
-      <c r="E758" t="inlineStr">
-        <is>
-          <t>ل</t>
-        </is>
-      </c>
-      <c r="F758" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
-      <c r="G758" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="H758" t="inlineStr">
-        <is>
-          <t>ن</t>
-        </is>
-      </c>
+      <c r="D758" t="inlineStr"/>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr"/>
       <c r="I758" t="inlineStr"/>
       <c r="J758" t="inlineStr"/>
       <c r="K758" t="inlineStr"/>
@@ -25485,28 +25497,16 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>loun</t>
+          <t>alan</t>
         </is>
       </c>
       <c r="B759" t="inlineStr"/>
       <c r="C759" t="inlineStr"/>
       <c r="D759" t="inlineStr"/>
-      <c r="E759" t="inlineStr">
-        <is>
-          <t>l</t>
-        </is>
-      </c>
-      <c r="F759" t="inlineStr">
-        <is>
-          <t>ou</t>
-        </is>
-      </c>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr"/>
       <c r="G759" t="inlineStr"/>
-      <c r="H759" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
+      <c r="H759" t="inlineStr"/>
       <c r="I759" t="inlineStr"/>
       <c r="J759" t="inlineStr"/>
       <c r="K759" t="inlineStr"/>
@@ -25541,7 +25541,7 @@
         </is>
       </c>
       <c r="B761" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C761" t="inlineStr"/>
       <c r="D761" t="inlineStr">
@@ -25564,12 +25564,12 @@
           <t>ا</t>
         </is>
       </c>
-      <c r="H761" t="inlineStr">
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
-      <c r="I761" t="inlineStr"/>
       <c r="J761" t="inlineStr"/>
       <c r="K761" t="inlineStr"/>
       <c r="L761" t="inlineStr"/>
@@ -25581,7 +25581,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>alwen</t>
+          <t>alwén</t>
         </is>
       </c>
       <c r="B762" t="inlineStr"/>
@@ -25601,17 +25601,17 @@
           <t>w</t>
         </is>
       </c>
-      <c r="G762" t="inlineStr">
-        <is>
-          <t>e</t>
-        </is>
-      </c>
+      <c r="G762" t="inlineStr"/>
       <c r="H762" t="inlineStr">
         <is>
+          <t>é</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
           <t>n</t>
         </is>
       </c>
-      <c r="I762" t="inlineStr"/>
       <c r="J762" t="inlineStr"/>
       <c r="K762" t="inlineStr"/>
       <c r="L762" t="inlineStr"/>
@@ -25749,7 +25749,7 @@
         </is>
       </c>
       <c r="B767" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C767" t="inlineStr"/>
       <c r="D767" t="inlineStr">
@@ -25772,12 +25772,12 @@
           <t>ا</t>
         </is>
       </c>
-      <c r="H767" t="inlineStr"/>
-      <c r="I767" t="inlineStr">
+      <c r="H767" t="inlineStr">
         <is>
           <t>ن</t>
         </is>
       </c>
+      <c r="I767" t="inlineStr"/>
       <c r="J767" t="inlineStr"/>
       <c r="K767" t="inlineStr"/>
       <c r="L767" t="inlineStr"/>
@@ -25789,7 +25789,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>alwén</t>
+          <t>alwen</t>
         </is>
       </c>
       <c r="B768" t="inlineStr"/>
@@ -25809,17 +25809,17 @@
           <t>w</t>
         </is>
       </c>
-      <c r="G768" t="inlineStr"/>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>é</t>
-        </is>
-      </c>
-      <c r="I768" t="inlineStr">
-        <is>
           <t>n</t>
         </is>
       </c>
+      <c r="I768" t="inlineStr"/>
       <c r="J768" t="inlineStr"/>
       <c r="K768" t="inlineStr"/>
       <c r="L768" t="inlineStr"/>
@@ -26021,7 +26021,7 @@
         </is>
       </c>
       <c r="B776" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="C776" t="inlineStr"/>
       <c r="D776" t="inlineStr">
@@ -26029,12 +26029,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="E776" t="inlineStr"/>
-      <c r="F776" t="inlineStr">
+      <c r="E776" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
+      <c r="F776" t="inlineStr"/>
       <c r="G776" t="inlineStr">
         <is>
           <t>ر</t>
@@ -26061,7 +26061,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>ma3rouf</t>
+          <t>maarouf</t>
         </is>
       </c>
       <c r="B777" t="inlineStr"/>
@@ -26078,7 +26078,7 @@
       </c>
       <c r="F777" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G777" t="inlineStr">
@@ -26129,7 +26129,7 @@
         </is>
       </c>
       <c r="B779" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="C779" t="inlineStr"/>
       <c r="D779" t="inlineStr">
@@ -26137,12 +26137,12 @@
           <t>م</t>
         </is>
       </c>
-      <c r="E779" t="inlineStr">
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr">
         <is>
           <t>ع</t>
         </is>
       </c>
-      <c r="F779" t="inlineStr"/>
       <c r="G779" t="inlineStr">
         <is>
           <t>ر</t>
@@ -26169,7 +26169,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>maarouf</t>
+          <t>ma3rouf</t>
         </is>
       </c>
       <c r="B780" t="inlineStr"/>
@@ -26186,7 +26186,7 @@
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
@@ -26257,7 +26257,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>wadi</t>
+          <t>seul</t>
         </is>
       </c>
       <c r="B783" t="inlineStr"/>
@@ -26321,7 +26321,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>seul</t>
+          <t>wadi</t>
         </is>
       </c>
       <c r="B786" t="inlineStr"/>
@@ -26365,7 +26365,7 @@
         </is>
       </c>
       <c r="B788" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C788" t="inlineStr"/>
       <c r="D788" t="inlineStr">
@@ -26401,7 +26401,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>wa7di</t>
+          <t>wahdy</t>
         </is>
       </c>
       <c r="B789" t="inlineStr"/>
@@ -26418,7 +26418,7 @@
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>h</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
@@ -26428,7 +26428,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="I789" t="inlineStr"/>
@@ -26465,7 +26465,7 @@
         </is>
       </c>
       <c r="B791" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C791" t="inlineStr"/>
       <c r="D791" t="inlineStr">
@@ -26501,7 +26501,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>wahdi</t>
+          <t>wa7di</t>
         </is>
       </c>
       <c r="B792" t="inlineStr"/>
@@ -26518,7 +26518,7 @@
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G792" t="inlineStr">
@@ -26568,27 +26568,11 @@
         <v>1</v>
       </c>
       <c r="C794" t="inlineStr"/>
-      <c r="D794" t="inlineStr">
-        <is>
-          <t>و</t>
-        </is>
-      </c>
+      <c r="D794" t="inlineStr"/>
       <c r="E794" t="inlineStr"/>
-      <c r="F794" t="inlineStr">
-        <is>
-          <t>ح</t>
-        </is>
-      </c>
-      <c r="G794" t="inlineStr">
-        <is>
-          <t>د</t>
-        </is>
-      </c>
-      <c r="H794" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr"/>
+      <c r="H794" t="inlineStr"/>
       <c r="I794" t="inlineStr"/>
       <c r="J794" t="inlineStr"/>
       <c r="K794" t="inlineStr"/>
@@ -26601,36 +26585,16 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>wahdy</t>
+          <t>bro7i</t>
         </is>
       </c>
       <c r="B795" t="inlineStr"/>
       <c r="C795" t="inlineStr"/>
-      <c r="D795" t="inlineStr">
-        <is>
-          <t>w</t>
-        </is>
-      </c>
-      <c r="E795" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F795" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="G795" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="H795" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
+      <c r="D795" t="inlineStr"/>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" t="inlineStr"/>
+      <c r="H795" t="inlineStr"/>
       <c r="I795" t="inlineStr"/>
       <c r="J795" t="inlineStr"/>
       <c r="K795" t="inlineStr"/>
@@ -26665,14 +26629,30 @@
         </is>
       </c>
       <c r="B797" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C797" t="inlineStr"/>
-      <c r="D797" t="inlineStr"/>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>و</t>
+        </is>
+      </c>
       <c r="E797" t="inlineStr"/>
-      <c r="F797" t="inlineStr"/>
-      <c r="G797" t="inlineStr"/>
-      <c r="H797" t="inlineStr"/>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>ح</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>د</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
       <c r="I797" t="inlineStr"/>
       <c r="J797" t="inlineStr"/>
       <c r="K797" t="inlineStr"/>
@@ -26685,16 +26665,36 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>bro7i</t>
+          <t>wahdi</t>
         </is>
       </c>
       <c r="B798" t="inlineStr"/>
       <c r="C798" t="inlineStr"/>
-      <c r="D798" t="inlineStr"/>
-      <c r="E798" t="inlineStr"/>
-      <c r="F798" t="inlineStr"/>
-      <c r="G798" t="inlineStr"/>
-      <c r="H798" t="inlineStr"/>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
       <c r="I798" t="inlineStr"/>
       <c r="J798" t="inlineStr"/>
       <c r="K798" t="inlineStr"/>
@@ -26829,7 +26829,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>pere</t>
+          <t>baba</t>
         </is>
       </c>
       <c r="B804" t="inlineStr"/>
@@ -26893,7 +26893,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>baba</t>
+          <t>pere</t>
         </is>
       </c>
       <c r="B807" t="inlineStr"/>
@@ -26937,7 +26937,7 @@
         </is>
       </c>
       <c r="B809" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C809" t="inlineStr"/>
       <c r="D809" t="inlineStr">
@@ -26973,7 +26973,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>weldi</t>
+          <t>waldy</t>
         </is>
       </c>
       <c r="B810" t="inlineStr"/>
@@ -26985,7 +26985,7 @@
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>a</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
@@ -27000,7 +27000,7 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>y</t>
         </is>
       </c>
       <c r="I810" t="inlineStr"/>
@@ -27037,7 +27037,7 @@
         </is>
       </c>
       <c r="B812" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C812" t="inlineStr"/>
       <c r="D812" t="inlineStr">
@@ -27073,7 +27073,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>waldy</t>
+          <t>weldi</t>
         </is>
       </c>
       <c r="B813" t="inlineStr"/>
@@ -27085,7 +27085,7 @@
       </c>
       <c r="E813" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F813" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>y</t>
+          <t>i</t>
         </is>
       </c>
       <c r="I813" t="inlineStr"/>
@@ -27301,39 +27301,15 @@
         </is>
       </c>
       <c r="B821" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C821" t="inlineStr"/>
-      <c r="D821" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="E821" t="inlineStr">
-        <is>
-          <t>ا</t>
-        </is>
-      </c>
-      <c r="F821" t="inlineStr">
-        <is>
-          <t>س</t>
-        </is>
-      </c>
-      <c r="G821" t="inlineStr">
-        <is>
-          <t>م</t>
-        </is>
-      </c>
-      <c r="H821" t="inlineStr">
-        <is>
-          <t>ي</t>
-        </is>
-      </c>
-      <c r="I821" t="inlineStr">
-        <is>
-          <t>ن</t>
-        </is>
-      </c>
+      <c r="D821" t="inlineStr"/>
+      <c r="E821" t="inlineStr"/>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="inlineStr"/>
       <c r="J821" t="inlineStr"/>
       <c r="K821" t="inlineStr"/>
       <c r="L821" t="inlineStr"/>
@@ -27345,41 +27321,17 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>yasmin</t>
+          <t>jasmin</t>
         </is>
       </c>
       <c r="B822" t="inlineStr"/>
       <c r="C822" t="inlineStr"/>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="E822" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="F822" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="G822" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="H822" t="inlineStr">
-        <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="I822" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
+      <c r="D822" t="inlineStr"/>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr"/>
+      <c r="I822" t="inlineStr"/>
       <c r="J822" t="inlineStr"/>
       <c r="K822" t="inlineStr"/>
       <c r="L822" t="inlineStr"/>
@@ -27413,15 +27365,39 @@
         </is>
       </c>
       <c r="B824" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C824" t="inlineStr"/>
-      <c r="D824" t="inlineStr"/>
-      <c r="E824" t="inlineStr"/>
-      <c r="F824" t="inlineStr"/>
-      <c r="G824" t="inlineStr"/>
-      <c r="H824" t="inlineStr"/>
-      <c r="I824" t="inlineStr"/>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>ا</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>س</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>م</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>ي</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>ن</t>
+        </is>
+      </c>
       <c r="J824" t="inlineStr"/>
       <c r="K824" t="inlineStr"/>
       <c r="L824" t="inlineStr"/>
@@ -27433,17 +27409,41 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>jasmin</t>
+          <t>yasmin</t>
         </is>
       </c>
       <c r="B825" t="inlineStr"/>
       <c r="C825" t="inlineStr"/>
-      <c r="D825" t="inlineStr"/>
-      <c r="E825" t="inlineStr"/>
-      <c r="F825" t="inlineStr"/>
-      <c r="G825" t="inlineStr"/>
-      <c r="H825" t="inlineStr"/>
-      <c r="I825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
       <c r="J825" t="inlineStr"/>
       <c r="K825" t="inlineStr"/>
       <c r="L825" t="inlineStr"/>
@@ -27925,7 +27925,7 @@
         </is>
       </c>
       <c r="B839" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C839" t="inlineStr"/>
       <c r="D839" t="inlineStr">
@@ -27961,7 +27961,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>yimchi</t>
+          <t>yemshi</t>
         </is>
       </c>
       <c r="B840" t="inlineStr"/>
@@ -27973,7 +27973,7 @@
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>e</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -27983,7 +27983,7 @@
       </c>
       <c r="G840" t="inlineStr">
         <is>
-          <t>ch</t>
+          <t>sh</t>
         </is>
       </c>
       <c r="H840" t="inlineStr">
@@ -28121,7 +28121,7 @@
         </is>
       </c>
       <c r="B845" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C845" t="inlineStr"/>
       <c r="D845" t="inlineStr">
@@ -28157,7 +28157,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>yemchi</t>
+          <t>yimchi</t>
         </is>
       </c>
       <c r="B846" t="inlineStr"/>
@@ -28169,7 +28169,7 @@
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>i</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
@@ -28221,7 +28221,7 @@
         </is>
       </c>
       <c r="B848" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C848" t="inlineStr"/>
       <c r="D848" t="inlineStr">
@@ -28257,7 +28257,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>yemshi</t>
+          <t>yemchi</t>
         </is>
       </c>
       <c r="B849" t="inlineStr"/>
@@ -28279,7 +28279,7 @@
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>sh</t>
+          <t>ch</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
@@ -28421,7 +28421,7 @@
         </is>
       </c>
       <c r="B854" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C854" t="inlineStr"/>
       <c r="D854" t="inlineStr">
@@ -28429,12 +28429,12 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="E854" t="inlineStr"/>
-      <c r="F854" t="inlineStr">
+      <c r="E854" t="inlineStr">
         <is>
           <t>ڤ</t>
         </is>
       </c>
+      <c r="F854" t="inlineStr"/>
       <c r="G854" t="inlineStr">
         <is>
           <t>د</t>
@@ -28457,7 +28457,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>yegdem</t>
+          <t>ygadém</t>
         </is>
       </c>
       <c r="B855" t="inlineStr"/>
@@ -28469,12 +28469,12 @@
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>g</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>a</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
@@ -28484,7 +28484,7 @@
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>e</t>
+          <t>é</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -28525,7 +28525,7 @@
         </is>
       </c>
       <c r="B857" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C857" t="inlineStr"/>
       <c r="D857" t="inlineStr">
@@ -28533,12 +28533,12 @@
           <t>ي</t>
         </is>
       </c>
-      <c r="E857" t="inlineStr">
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr">
         <is>
           <t>ڤ</t>
         </is>
       </c>
-      <c r="F857" t="inlineStr"/>
       <c r="G857" t="inlineStr">
         <is>
           <t>د</t>
@@ -28561,7 +28561,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>ygadem</t>
+          <t>yegdem</t>
         </is>
       </c>
       <c r="B858" t="inlineStr"/>
@@ -28573,12 +28573,12 @@
       </c>
       <c r="E858" t="inlineStr">
         <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
           <t>g</t>
-        </is>
-      </c>
-      <c r="F858" t="inlineStr">
-        <is>
-          <t>a</t>
         </is>
       </c>
       <c r="G858" t="inlineStr">
@@ -28665,7 +28665,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>ygadém</t>
+          <t>ygadam</t>
         </is>
       </c>
       <c r="B861" t="inlineStr"/>
@@ -28692,7 +28692,7 @@
       </c>
       <c r="H861" t="inlineStr">
         <is>
-          <t>é</t>
+          <t>a</t>
         </is>
       </c>
       <c r="I861" t="inlineStr">
@@ -28837,7 +28837,7 @@
         </is>
       </c>
       <c r="B866" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C866" t="inlineStr"/>
       <c r="D866" t="inlineStr">
@@ -28873,7 +28873,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>ygadam</t>
+          <t>ygadem</t>
         </is>
       </c>
       <c r="B867" t="inlineStr"/>
@@ -28900,7 +28900,7 @@
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>e</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
